--- a/setting.xlsx
+++ b/setting.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\github\survey-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B70EDAF9-F608-4AC7-9C11-6AD609B450FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE39DFB1-B365-44EF-9A3A-33F69C4F9803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4635" yWindow="4635" windowWidth="38700" windowHeight="15345" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10035" yWindow="3900" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="受験者名簿" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="59">
   <si>
     <t>山田 太郎</t>
   </si>
@@ -58,101 +58,151 @@
     <t>加藤 雅治</t>
   </si>
   <si>
+    <t>正答表示</t>
+  </si>
+  <si>
+    <t>問題番号   </t>
+  </si>
+  <si>
+    <t>領域   </t>
+  </si>
+  <si>
+    <t>正答   </t>
+  </si>
+  <si>
+    <t>Q1   </t>
+  </si>
+  <si>
+    <t>計算   </t>
+  </si>
+  <si>
+    <t>ア   </t>
+  </si>
+  <si>
+    <t>Q2   </t>
+  </si>
+  <si>
+    <t>イ   </t>
+  </si>
+  <si>
+    <t>Q3   </t>
+  </si>
+  <si>
+    <t>ウ   </t>
+  </si>
+  <si>
+    <t>Q4   </t>
+  </si>
+  <si>
+    <t>読解   </t>
+  </si>
+  <si>
+    <t>Q5   </t>
+  </si>
+  <si>
+    <t>Q6   </t>
+  </si>
+  <si>
+    <t>Q7   </t>
+  </si>
+  <si>
+    <t>漢字   </t>
+  </si>
+  <si>
+    <t>Q8   </t>
+  </si>
+  <si>
+    <t>Q9   </t>
+  </si>
+  <si>
+    <t>語彙   </t>
+  </si>
+  <si>
+    <t>Q10   </t>
+  </si>
+  <si>
+    <t>エ   </t>
+  </si>
+  <si>
+    <t>Q11   </t>
+  </si>
+  <si>
+    <t>資料活用   </t>
+  </si>
+  <si>
+    <t>Q12   </t>
+  </si>
+  <si>
+    <t>Q13   </t>
+  </si>
+  <si>
+    <t>短答   </t>
+  </si>
+  <si>
+    <t>月曜日   </t>
+  </si>
+  <si>
+    <t>Q14   </t>
+  </si>
+  <si>
+    <t>バス   </t>
+  </si>
+  <si>
+    <t>Q15   </t>
+  </si>
+  <si>
+    <t>長文記述       </t>
+  </si>
+  <si>
     <t>答案番号</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>氏名</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>問題番号</t>
-    <rPh sb="0" eb="2">
-      <t>モンダイ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>バンゴウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>カテゴリ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Q1</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Q2</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Q3</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Q4</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Q5</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Q6</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Q7</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Q8</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Q9</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Q10</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>計算</t>
-    <rPh sb="0" eb="2">
-      <t>ケイサン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>読解</t>
-    <rPh sb="0" eb="2">
-      <t>ドッカイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>漢字</t>
-    <rPh sb="0" eb="2">
-      <t>カンジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>語彙</t>
-    <rPh sb="0" eb="2">
-      <t>ゴイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>記述</t>
-    <rPh sb="0" eb="2">
-      <t>キジュツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>所属グループ</t>
+  </si>
+  <si>
+    <t>1組</t>
+  </si>
+  <si>
+    <t>2組</t>
+  </si>
+  <si>
+    <t>吉田 美咲</t>
+  </si>
+  <si>
+    <t>3組</t>
+  </si>
+  <si>
+    <t>山本 拓也</t>
+  </si>
+  <si>
+    <t>松本 彩</t>
+  </si>
+  <si>
+    <t>井上 大輔</t>
+  </si>
+  <si>
+    <t>林 優子</t>
+  </si>
+  <si>
+    <t>清水 健</t>
+  </si>
+  <si>
+    <t>4組</t>
+  </si>
+  <si>
+    <t>斎藤 真由</t>
+  </si>
+  <si>
+    <t>森 翔太</t>
+  </si>
+  <si>
+    <t>池田 奈々</t>
+  </si>
+  <si>
+    <t>橋本 亮</t>
   </si>
 </sst>
 </file>
@@ -477,95 +527,238 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>43</v>
+      </c>
+      <c r="C1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
+      <c r="C2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
+      <c r="C3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
+      <c r="C4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:2">
+      <c r="C5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:2">
+      <c r="C6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:2">
+      <c r="C7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:2">
+      <c r="C8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:2">
+      <c r="C9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:2">
+      <c r="C10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
+      </c>
+      <c r="C11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -576,99 +769,233 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAAD0246-A0C4-4F3B-9897-BC6C42F0A69D}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s">
         <v>12</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="D1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
         <v>16</v>
       </c>
-      <c r="B4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
+      <c r="D8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
         <v>18</v>
       </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
+      <c r="D9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
         <v>20</v>
       </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+      <c r="D10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/setting.xlsx
+++ b/setting.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\github\survey-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE39DFB1-B365-44EF-9A3A-33F69C4F9803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA36F40F-0742-4FFB-B880-5A6B355BE77A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10035" yWindow="3900" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="受験者名簿" sheetId="1" r:id="rId1"/>
@@ -26,134 +26,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="59">
-  <si>
-    <t>山田 太郎</t>
-  </si>
-  <si>
-    <t>佐藤 花子</t>
-  </si>
-  <si>
-    <t>田中 一郎</t>
-  </si>
-  <si>
-    <t>鈴木 京子</t>
-  </si>
-  <si>
-    <t>高橋 健太</t>
-  </si>
-  <si>
-    <t>渡辺 直美</t>
-  </si>
-  <si>
-    <t>伊藤 博</t>
-  </si>
-  <si>
-    <t>中村 恵</t>
-  </si>
-  <si>
-    <t>小林 隆</t>
-  </si>
-  <si>
-    <t>加藤 雅治</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="58">
   <si>
     <t>正答表示</t>
   </si>
   <si>
-    <t>問題番号   </t>
-  </si>
-  <si>
-    <t>領域   </t>
-  </si>
-  <si>
-    <t>正答   </t>
-  </si>
-  <si>
-    <t>Q1   </t>
-  </si>
-  <si>
-    <t>計算   </t>
-  </si>
-  <si>
-    <t>ア   </t>
-  </si>
-  <si>
-    <t>Q2   </t>
-  </si>
-  <si>
-    <t>イ   </t>
-  </si>
-  <si>
-    <t>Q3   </t>
-  </si>
-  <si>
-    <t>ウ   </t>
-  </si>
-  <si>
-    <t>Q4   </t>
-  </si>
-  <si>
-    <t>読解   </t>
-  </si>
-  <si>
-    <t>Q5   </t>
-  </si>
-  <si>
-    <t>Q6   </t>
-  </si>
-  <si>
-    <t>Q7   </t>
-  </si>
-  <si>
-    <t>漢字   </t>
-  </si>
-  <si>
-    <t>Q8   </t>
-  </si>
-  <si>
-    <t>Q9   </t>
-  </si>
-  <si>
-    <t>語彙   </t>
-  </si>
-  <si>
-    <t>Q10   </t>
-  </si>
-  <si>
-    <t>エ   </t>
-  </si>
-  <si>
-    <t>Q11   </t>
-  </si>
-  <si>
-    <t>資料活用   </t>
-  </si>
-  <si>
-    <t>Q12   </t>
-  </si>
-  <si>
-    <t>Q13   </t>
-  </si>
-  <si>
-    <t>短答   </t>
-  </si>
-  <si>
-    <t>月曜日   </t>
-  </si>
-  <si>
-    <t>Q14   </t>
-  </si>
-  <si>
-    <t>バス   </t>
-  </si>
-  <si>
-    <t>Q15   </t>
-  </si>
-  <si>
-    <t>長文記述       </t>
-  </si>
-  <si>
     <t>答案番号</t>
   </si>
   <si>
@@ -169,40 +46,160 @@
     <t>2組</t>
   </si>
   <si>
-    <t>吉田 美咲</t>
-  </si>
-  <si>
     <t>3組</t>
   </si>
   <si>
-    <t>山本 拓也</t>
-  </si>
-  <si>
-    <t>松本 彩</t>
-  </si>
-  <si>
-    <t>井上 大輔</t>
-  </si>
-  <si>
-    <t>林 優子</t>
-  </si>
-  <si>
-    <t>清水 健</t>
-  </si>
-  <si>
-    <t>4組</t>
-  </si>
-  <si>
-    <t>斎藤 真由</t>
-  </si>
-  <si>
-    <t>森 翔太</t>
-  </si>
-  <si>
-    <t>池田 奈々</t>
-  </si>
-  <si>
-    <t>橋本 亮</t>
+    <t>山田太郎</t>
+  </si>
+  <si>
+    <t>佐藤花子</t>
+  </si>
+  <si>
+    <t>鈴木一郎</t>
+  </si>
+  <si>
+    <t>高橋美咲</t>
+  </si>
+  <si>
+    <t>田中健</t>
+  </si>
+  <si>
+    <t>伊藤彩</t>
+  </si>
+  <si>
+    <t>渡辺翔</t>
+  </si>
+  <si>
+    <t>小林咲</t>
+  </si>
+  <si>
+    <t>加藤大輔</t>
+  </si>
+  <si>
+    <t>吉田優子</t>
+  </si>
+  <si>
+    <t>山本直樹</t>
+  </si>
+  <si>
+    <t>中村萌</t>
+  </si>
+  <si>
+    <t>松本陽介</t>
+  </si>
+  <si>
+    <t>井上愛</t>
+  </si>
+  <si>
+    <t>木村拓海</t>
+  </si>
+  <si>
+    <t>問題番号</t>
+  </si>
+  <si>
+    <t>領域</t>
+  </si>
+  <si>
+    <t>正答</t>
+  </si>
+  <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>数と式</t>
+  </si>
+  <si>
+    <t>Q2</t>
+  </si>
+  <si>
+    <t>Q3</t>
+  </si>
+  <si>
+    <t>Q4</t>
+  </si>
+  <si>
+    <t>Q5</t>
+  </si>
+  <si>
+    <t>Q6</t>
+  </si>
+  <si>
+    <t>図形</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Q7</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>Q8</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Q9</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>Q10</t>
+  </si>
+  <si>
+    <t>Q11</t>
+  </si>
+  <si>
+    <t>関数</t>
+  </si>
+  <si>
+    <t>Q12</t>
+  </si>
+  <si>
+    <t>Q13</t>
+  </si>
+  <si>
+    <t>Q14</t>
+  </si>
+  <si>
+    <t>Q15</t>
+  </si>
+  <si>
+    <t>Q16</t>
+  </si>
+  <si>
+    <t>データの活用</t>
+  </si>
+  <si>
+    <t>平均</t>
+  </si>
+  <si>
+    <t>Q17</t>
+  </si>
+  <si>
+    <t>中央値</t>
+  </si>
+  <si>
+    <t>Q18</t>
+  </si>
+  <si>
+    <t>最頻値</t>
+  </si>
+  <si>
+    <t>Q19</t>
+  </si>
+  <si>
+    <t>範囲</t>
+  </si>
+  <si>
+    <t>Q20</t>
+  </si>
+  <si>
+    <t>分散</t>
   </si>
 </sst>
 </file>
@@ -527,18 +524,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>44</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -546,10 +543,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -557,10 +554,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -568,10 +565,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -579,10 +576,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -590,10 +587,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -601,10 +598,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
         <v>5</v>
-      </c>
-      <c r="C7" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -612,10 +609,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
         <v>6</v>
-      </c>
-      <c r="C8" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -623,10 +620,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -634,10 +631,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -645,10 +642,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -656,10 +653,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -667,10 +664,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -678,10 +675,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>48</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -689,10 +686,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -700,65 +697,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>53</v>
-      </c>
-      <c r="C17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" t="s">
-        <v>55</v>
-      </c>
-      <c r="C18" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" t="s">
-        <v>56</v>
-      </c>
-      <c r="C19" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20" t="s">
-        <v>57</v>
-      </c>
-      <c r="C20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>58</v>
-      </c>
-      <c r="C21" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -769,32 +711,32 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAAD0246-A0C4-4F3B-9897-BC6C42F0A69D}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
+        <v>26</v>
+      </c>
+      <c r="C2">
+        <v>5</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -802,13 +744,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
+        <v>26</v>
+      </c>
+      <c r="C3">
+        <v>12</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -816,13 +758,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
+        <v>26</v>
+      </c>
+      <c r="C4">
+        <v>8</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -830,13 +772,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
+        <v>26</v>
+      </c>
+      <c r="C5">
+        <v>15</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -844,13 +786,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
+        <v>26</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -858,13 +800,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -872,13 +814,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -886,13 +828,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -900,13 +842,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -914,27 +856,27 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" t="s">
-        <v>16</v>
+        <v>42</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -942,13 +884,13 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" t="s">
-        <v>18</v>
+        <v>42</v>
+      </c>
+      <c r="C13">
+        <v>-1</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -956,13 +898,13 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" t="s">
-        <v>37</v>
+        <v>42</v>
+      </c>
+      <c r="C14">
+        <v>4</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -970,13 +912,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" t="s">
-        <v>39</v>
+        <v>42</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -984,13 +926,86 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
